--- a/messplan.xlsx
+++ b/messplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Desktop\Studium\Laufend\Mechatronik und Leistungselektronik Projekt VU\project_code\orbitalPropagatorComparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69980A80-9CDE-489F-B39F-426FDD88AB96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E52B78-6C42-4500-9197-AE8ECD027053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
   <si>
     <t>STARLINK-1298</t>
   </si>
@@ -156,6 +156,15 @@
   </si>
   <si>
     <t>StARLINK-1318</t>
+  </si>
+  <si>
+    <t>SL-16 R/B</t>
+  </si>
+  <si>
+    <t>23343U</t>
+  </si>
+  <si>
+    <t>30222U</t>
   </si>
 </sst>
 </file>
@@ -481,7 +490,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.6640625" customWidth="1"/>
@@ -552,7 +561,7 @@
         <v>3.62</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E18" si="0">SUM(C4,D4)</f>
+        <f t="shared" ref="E4:E20" si="0">SUM(C4,D4)</f>
         <v>10.620000000000001</v>
       </c>
       <c r="F4" t="s">
@@ -829,7 +838,7 @@
         <v>115.64</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -851,6 +860,48 @@
       </c>
       <c r="F18" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C19" s="1">
+        <v>128.19</v>
+      </c>
+      <c r="D19" s="1">
+        <v>4.79</v>
+      </c>
+      <c r="E19" s="1">
+        <f t="shared" si="0"/>
+        <v>132.97999999999999</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="1">
+        <v>142.21</v>
+      </c>
+      <c r="D20" s="1">
+        <v>6.68</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="0"/>
+        <v>148.89000000000001</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/messplan.xlsx
+++ b/messplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Desktop\Studium\Laufend\Mechatronik und Leistungselektronik Projekt VU\project_code\orbitalPropagatorComparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60E52B78-6C42-4500-9197-AE8ECD027053}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3D9009-6CF9-4324-89C2-3AD4327BD4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
   <si>
     <t>STARLINK-1298</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>30222U</t>
+  </si>
+  <si>
+    <t>30577U</t>
   </si>
 </sst>
 </file>
@@ -206,10 +209,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -490,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.6640625" customWidth="1"/>
@@ -561,7 +563,7 @@
         <v>3.62</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E20" si="0">SUM(C4,D4)</f>
+        <f t="shared" ref="E4:E21" si="0">SUM(C4,D4)</f>
         <v>10.620000000000001</v>
       </c>
       <c r="F4" t="s">
@@ -820,24 +822,24 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17">
         <v>105.62</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17">
         <v>10.02</v>
       </c>
-      <c r="E17" s="2">
+      <c r="E17">
         <f t="shared" si="0"/>
         <v>115.64</v>
       </c>
-      <c r="F17" s="2" t="s">
+      <c r="F17" t="s">
         <v>20</v>
       </c>
     </row>
@@ -902,6 +904,27 @@
       </c>
       <c r="F20" s="1" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21">
+        <v>155.88</v>
+      </c>
+      <c r="D21">
+        <v>6.25</v>
+      </c>
+      <c r="E21">
+        <f t="shared" si="0"/>
+        <v>162.13</v>
+      </c>
+      <c r="F21" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/messplan.xlsx
+++ b/messplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Desktop\Studium\Laufend\Mechatronik und Leistungselektronik Projekt VU\project_code\orbitalPropagatorComparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E3D9009-6CF9-4324-89C2-3AD4327BD4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C256EB42-3941-4BC9-B497-7A51B6BAB608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -183,7 +183,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -193,6 +193,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -209,9 +215,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -492,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.6640625" customWidth="1"/>
@@ -503,12 +510,12 @@
     <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -528,7 +535,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -549,7 +556,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -570,7 +577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -591,7 +598,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
@@ -612,7 +619,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -633,7 +640,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -654,7 +661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -675,7 +682,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -696,7 +703,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -717,7 +724,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -738,7 +745,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -758,8 +765,9 @@
       <c r="F13" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -780,7 +788,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -801,7 +809,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>17</v>
       </c>

--- a/messplan.xlsx
+++ b/messplan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Desktop\Studium\Laufend\Mechatronik und Leistungselektronik Projekt VU\project_code\orbitalPropagatorComparison\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\alexander_dvorak\orbitalPropagator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C256EB42-3941-4BC9-B497-7A51B6BAB608}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0024E01-95B6-49DD-9419-12E7EFFD5F35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="17985" yWindow="4170" windowWidth="19590" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monda_19JAN2026UTC16_55" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="46">
   <si>
     <t>STARLINK-1298</t>
   </si>
@@ -168,6 +168,12 @@
   </si>
   <si>
     <t>30577U</t>
+  </si>
+  <si>
+    <t>CZ-4 DEB</t>
+  </si>
+  <si>
+    <t>23261U</t>
   </si>
 </sst>
 </file>
@@ -183,7 +189,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -202,6 +208,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -215,10 +227,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -499,23 +512,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="53.6640625" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="53.7109375" customWidth="1"/>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -535,7 +548,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -556,7 +569,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -570,14 +583,14 @@
         <v>3.62</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E21" si="0">SUM(C4,D4)</f>
+        <f t="shared" ref="E4:E22" si="0">SUM(C4,D4)</f>
         <v>10.620000000000001</v>
       </c>
       <c r="F4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -598,7 +611,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>39</v>
       </c>
@@ -619,7 +632,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -640,7 +653,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -661,7 +674,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
@@ -682,7 +695,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
@@ -703,7 +716,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -724,7 +737,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
@@ -745,7 +758,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>14</v>
       </c>
@@ -767,7 +780,7 @@
       </c>
       <c r="G13" s="2"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -787,8 +800,9 @@
       <c r="F14" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="G14" s="2"/>
+    </row>
+    <row r="15" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>16</v>
       </c>
@@ -808,8 +822,9 @@
       <c r="F15" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="G15" s="2"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -829,8 +844,9 @@
       <c r="F16" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>13</v>
       </c>
@@ -850,90 +866,117 @@
       <c r="F17" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C18" s="1">
+        <v>115.75</v>
+      </c>
+      <c r="D18" s="1">
+        <v>4.67</v>
+      </c>
+      <c r="E18" s="1">
+        <f t="shared" si="0"/>
+        <v>120.42</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G18" s="2"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>18</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>32</v>
       </c>
-      <c r="C18">
+      <c r="C19">
         <v>120.15</v>
       </c>
-      <c r="D18">
+      <c r="D19">
         <v>7.29</v>
       </c>
-      <c r="E18">
+      <c r="E19">
         <f t="shared" si="0"/>
         <v>127.44000000000001</v>
       </c>
-      <c r="F18" t="s">
+      <c r="F19" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="G19" s="3"/>
+    </row>
+    <row r="20" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="1">
+      <c r="C20" s="1">
         <v>128.19</v>
       </c>
-      <c r="D19" s="1">
+      <c r="D20" s="1">
         <v>4.79</v>
       </c>
-      <c r="E19" s="1">
+      <c r="E20" s="1">
         <f t="shared" si="0"/>
         <v>132.97999999999999</v>
       </c>
-      <c r="F19" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="F20" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G20" s="3"/>
+    </row>
+    <row r="21" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B21" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="1">
+      <c r="C21" s="1">
         <v>142.21</v>
       </c>
-      <c r="D20" s="1">
+      <c r="D21" s="1">
         <v>6.68</v>
       </c>
-      <c r="E20" s="1">
+      <c r="E21" s="1">
         <f t="shared" si="0"/>
         <v>148.89000000000001</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" t="s">
+      <c r="F21" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="G21" s="3"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>12</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C21">
+      <c r="C22">
         <v>155.88</v>
       </c>
-      <c r="D21">
+      <c r="D22">
         <v>6.25</v>
       </c>
-      <c r="E21">
+      <c r="E22">
         <f t="shared" si="0"/>
         <v>162.13</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F22" t="s">
         <v>20</v>
       </c>
+      <c r="G22" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/messplan.xlsx
+++ b/messplan.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Desktop\Studium\Laufend\Mechatronik und Leistungselektronik Projekt VU\project_code\orbitalPropagatorComparison\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\alexander_dvorak\orbitalPropagator\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DFA4D83-2926-4F3C-9EB1-E4AB4A7F251F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3335B01F-8C89-46F6-A6B5-1E37ECE13142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-6750" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28905" yWindow="-6630" windowWidth="16680" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monday_19JAN2026UTC15_55" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
   <si>
     <t>Satellite</t>
   </si>
@@ -57,9 +57,6 @@
     <t>DELTA 1 DEB</t>
   </si>
   <si>
-    <t>CZ-4B DEB</t>
-  </si>
-  <si>
     <t>COSMOS 2170</t>
   </si>
   <si>
@@ -84,9 +81,6 @@
     <t>55176U</t>
   </si>
   <si>
-    <t>29215U</t>
-  </si>
-  <si>
     <t>45442U</t>
   </si>
   <si>
@@ -103,6 +97,63 @@
   </si>
   <si>
     <t>Tuesday 20.01.2026, 16:00 UTC</t>
+  </si>
+  <si>
+    <t>Indicator:</t>
+  </si>
+  <si>
+    <t>comment</t>
+  </si>
+  <si>
+    <t>Teil am Anfang leer, rest super</t>
+  </si>
+  <si>
+    <t>super</t>
+  </si>
+  <si>
+    <t>Satellit nur im abgsteigenden Teil sichtbar</t>
+  </si>
+  <si>
+    <t>12217U</t>
+  </si>
+  <si>
+    <t>SL-8 R/B</t>
+  </si>
+  <si>
+    <t>13034U</t>
+  </si>
+  <si>
+    <t>KITSAT 3</t>
+  </si>
+  <si>
+    <t>25756U</t>
+  </si>
+  <si>
+    <t>ONEWEB-0399</t>
+  </si>
+  <si>
+    <t>50479U</t>
+  </si>
+  <si>
+    <t>NOAA 6</t>
+  </si>
+  <si>
+    <t>11416U</t>
+  </si>
+  <si>
+    <t>comment:</t>
+  </si>
+  <si>
+    <t>Satellit nur in mittlerem Teilfenster sichtbar, aber rund um Switch</t>
+  </si>
+  <si>
+    <t>Satellit kaum bzw nur recht selten sichtbar, aber vor und nach Switch</t>
+  </si>
+  <si>
+    <t>Super</t>
+  </si>
+  <si>
+    <t>Blinderfleck dabei, aber sonst gut</t>
   </si>
 </sst>
 </file>
@@ -441,7 +492,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="53.6640625" customWidth="1"/>
@@ -450,19 +501,20 @@
     <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="37.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -476,138 +528,137 @@
       <c r="F2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="1">
-        <v>71.92</v>
-      </c>
-      <c r="D3" s="1">
-        <v>6.51</v>
-      </c>
-      <c r="E3" s="1">
-        <f t="shared" ref="E3:E8" si="0">SUM(C3,D3)</f>
-        <v>78.430000000000007</v>
-      </c>
-      <c r="F3" s="1" t="s">
+      <c r="C3">
+        <v>79.78</v>
+      </c>
+      <c r="D3">
+        <v>5.47</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E7" si="0">SUM(C3,D3)</f>
+        <v>85.25</v>
+      </c>
+      <c r="F3" t="s">
         <v>10</v>
       </c>
-      <c r="G3" s="3"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+      <c r="G3" s="2"/>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>79.78</v>
-      </c>
-      <c r="D4">
-        <v>5.47</v>
-      </c>
-      <c r="E4">
-        <f t="shared" si="0"/>
-        <v>85.25</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="1">
+      <c r="B4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="1">
         <v>87.19</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D4" s="1">
         <v>6.43</v>
       </c>
-      <c r="E5" s="1">
+      <c r="E4" s="1">
         <f t="shared" si="0"/>
         <v>93.62</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="2"/>
+      <c r="H4" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5">
+        <v>95.28</v>
+      </c>
+      <c r="D5">
+        <v>7.19</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>102.47</v>
+      </c>
+      <c r="F5" t="s">
         <v>10</v>
       </c>
       <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C6">
-        <v>95.28</v>
+        <v>105.62</v>
       </c>
       <c r="D6">
-        <v>7.19</v>
+        <v>10.02</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>102.47</v>
+        <v>115.64</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7">
-        <v>105.62</v>
-      </c>
-      <c r="D7">
-        <v>10.02</v>
-      </c>
-      <c r="E7">
-        <f t="shared" si="0"/>
-        <v>115.64</v>
-      </c>
-      <c r="F7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="1">
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" s="1">
         <v>115.75</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D7" s="1">
         <v>4.67</v>
       </c>
-      <c r="E8" s="1">
+      <c r="E7" s="1">
         <f t="shared" si="0"/>
         <v>120.42</v>
       </c>
-      <c r="F8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="3"/>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="3"/>
+      <c r="H7" s="1" t="s">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -616,25 +667,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{204148D0-CE3C-4A39-93CB-9E0152AEB5C3}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="26.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="57.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
         <v>1</v>
@@ -647,6 +700,162 @@
       </c>
       <c r="F2" t="s">
         <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3">
+        <v>0.45</v>
+      </c>
+      <c r="D3">
+        <v>10.37</v>
+      </c>
+      <c r="E3">
+        <f>SUM(C3,D3)</f>
+        <v>10.819999999999999</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="1">
+        <v>18.260000000000002</v>
+      </c>
+      <c r="D4" s="1">
+        <v>4.8</v>
+      </c>
+      <c r="E4" s="1">
+        <f t="shared" ref="E4:E8" si="0">SUM(C4,D4)</f>
+        <v>23.060000000000002</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="3"/>
+      <c r="H4" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5">
+        <v>56.6</v>
+      </c>
+      <c r="D5">
+        <v>6.72</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="0"/>
+        <v>63.32</v>
+      </c>
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G5" s="2"/>
+      <c r="H5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="1">
+        <v>74.97</v>
+      </c>
+      <c r="D6" s="1">
+        <v>5.0199999999999996</v>
+      </c>
+      <c r="E6" s="1">
+        <f t="shared" si="0"/>
+        <v>79.989999999999995</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G6" s="2"/>
+      <c r="H6" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7" s="1">
+        <v>82.38</v>
+      </c>
+      <c r="D7" s="1">
+        <v>6.91</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="0"/>
+        <v>89.289999999999992</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G7" s="2"/>
+      <c r="H7" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="1">
+        <v>106.09</v>
+      </c>
+      <c r="D8" s="1">
+        <v>5.89</v>
+      </c>
+      <c r="E8" s="1">
+        <f t="shared" si="0"/>
+        <v>111.98</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="1" t="s">
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/messplan.xlsx
+++ b/messplan.xlsx
@@ -5,16 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="U:\alexander_dvorak\orbitalPropagator\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Desktop\Studium\Laufend\Mechatronik und Leistungselektronik Projekt VU\project_code\orbitalPropagatorComparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3335B01F-8C89-46F6-A6B5-1E37ECE13142}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801E7233-45AF-461F-8263-C9365B688A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28905" yWindow="-6630" windowWidth="16680" windowHeight="15585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="11700" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monday_19JAN2026UTC15_55" sheetId="1" r:id="rId1"/>
     <sheet name="Tuesday_20_JAN2026UTC16_00" sheetId="2" r:id="rId2"/>
+    <sheet name="Monday_26JAN2026UTC16_00" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="56">
   <si>
     <t>Satellite</t>
   </si>
@@ -154,6 +155,57 @@
   </si>
   <si>
     <t>Blinderfleck dabei, aber sonst gut</t>
+  </si>
+  <si>
+    <t>40028U</t>
+  </si>
+  <si>
+    <t>39208U</t>
+  </si>
+  <si>
+    <t>58992U</t>
+  </si>
+  <si>
+    <t>26351I</t>
+  </si>
+  <si>
+    <t>44322U</t>
+  </si>
+  <si>
+    <t>43071U</t>
+  </si>
+  <si>
+    <t>NOAA 9</t>
+  </si>
+  <si>
+    <t>SL-14 R/B</t>
+  </si>
+  <si>
+    <t>43011U</t>
+  </si>
+  <si>
+    <t>13114U</t>
+  </si>
+  <si>
+    <t>HEAD-1</t>
+  </si>
+  <si>
+    <t>15427U</t>
+  </si>
+  <si>
+    <t>IRIDIUM 138</t>
+  </si>
+  <si>
+    <t>RCM 1</t>
+  </si>
+  <si>
+    <t>ADRAS-J</t>
+  </si>
+  <si>
+    <t>PAYLOAD A</t>
+  </si>
+  <si>
+    <t>POPSAT HIP 1</t>
   </si>
 </sst>
 </file>
@@ -861,4 +913,242 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2806803F-56BF-4E65-BE1E-5B4E77DD970E}">
+  <dimension ref="A1:H11"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="26.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="1">
+        <v>2.79</v>
+      </c>
+      <c r="D3" s="1">
+        <v>3.93</v>
+      </c>
+      <c r="E3" s="1">
+        <f>SUM(C3,D3)</f>
+        <v>6.7200000000000006</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>54</v>
+      </c>
+      <c r="B4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4">
+        <v>12.17</v>
+      </c>
+      <c r="D4">
+        <v>4.9000000000000004</v>
+      </c>
+      <c r="E4">
+        <f t="shared" ref="E4:E22" si="0">SUM(C4,D4)</f>
+        <v>17.07</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" s="1">
+        <v>19.28</v>
+      </c>
+      <c r="D5" s="1">
+        <v>4.01</v>
+      </c>
+      <c r="E5" s="1">
+        <f t="shared" si="0"/>
+        <v>23.29</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6">
+        <v>25.35</v>
+      </c>
+      <c r="D6">
+        <v>3.96</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="0"/>
+        <v>29.310000000000002</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="1">
+        <v>32.81</v>
+      </c>
+      <c r="D7" s="1">
+        <v>4.46</v>
+      </c>
+      <c r="E7" s="1">
+        <f t="shared" si="0"/>
+        <v>37.270000000000003</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8">
+        <v>39.31</v>
+      </c>
+      <c r="D8">
+        <v>5.32</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="0"/>
+        <v>44.63</v>
+      </c>
+      <c r="F8" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C9" s="1">
+        <v>47.51</v>
+      </c>
+      <c r="D9" s="1">
+        <v>6.07</v>
+      </c>
+      <c r="E9" s="1">
+        <f t="shared" si="0"/>
+        <v>53.58</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10">
+        <v>57.14</v>
+      </c>
+      <c r="D10">
+        <v>6.98</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="0"/>
+        <v>64.12</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="1">
+        <v>69.22</v>
+      </c>
+      <c r="D11" s="1">
+        <v>5.22</v>
+      </c>
+      <c r="E11" s="1">
+        <f t="shared" si="0"/>
+        <v>74.44</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/messplan.xlsx
+++ b/messplan.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Desktop\Studium\Laufend\Mechatronik und Leistungselektronik Projekt VU\project_code\orbitalPropagatorComparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{801E7233-45AF-461F-8263-C9365B688A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF350AAF-77BC-468D-9C65-13B2665327A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="11700" windowHeight="15585" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monday_19JAN2026UTC15_55" sheetId="1" r:id="rId1"/>
     <sheet name="Tuesday_20_JAN2026UTC16_00" sheetId="2" r:id="rId2"/>
-    <sheet name="Monday_26JAN2026UTC16_00" sheetId="3" r:id="rId3"/>
+    <sheet name="Wednesday_17FEB2026UTC04_00" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="59">
   <si>
     <t>Satellite</t>
   </si>
@@ -157,62 +157,71 @@
     <t>Blinderfleck dabei, aber sonst gut</t>
   </si>
   <si>
-    <t>40028U</t>
-  </si>
-  <si>
-    <t>39208U</t>
-  </si>
-  <si>
-    <t>58992U</t>
-  </si>
-  <si>
-    <t>26351I</t>
-  </si>
-  <si>
-    <t>44322U</t>
-  </si>
-  <si>
-    <t>43071U</t>
-  </si>
-  <si>
-    <t>NOAA 9</t>
-  </si>
-  <si>
-    <t>SL-14 R/B</t>
-  </si>
-  <si>
-    <t>43011U</t>
-  </si>
-  <si>
-    <t>13114U</t>
-  </si>
-  <si>
-    <t>HEAD-1</t>
-  </si>
-  <si>
-    <t>15427U</t>
-  </si>
-  <si>
-    <t>IRIDIUM 138</t>
-  </si>
-  <si>
-    <t>RCM 1</t>
-  </si>
-  <si>
-    <t>ADRAS-J</t>
-  </si>
-  <si>
-    <t>PAYLOAD A</t>
-  </si>
-  <si>
-    <t>POPSAT HIP 1</t>
+    <t>OBJECT B</t>
+  </si>
+  <si>
+    <t>49316U</t>
+  </si>
+  <si>
+    <t>CSG-1</t>
+  </si>
+  <si>
+    <t>44873U</t>
+  </si>
+  <si>
+    <t>COSMO SKYMED FM3</t>
+  </si>
+  <si>
+    <t>67304U</t>
+  </si>
+  <si>
+    <t>SAOCOM 1-A</t>
+  </si>
+  <si>
+    <t>43641U</t>
+  </si>
+  <si>
+    <t>SARAL</t>
+  </si>
+  <si>
+    <t>39086U</t>
+  </si>
+  <si>
+    <t>COSMOS 2355</t>
+  </si>
+  <si>
+    <t>25366U</t>
+  </si>
+  <si>
+    <t>YUNHAI 3-02</t>
+  </si>
+  <si>
+    <t>59343U</t>
+  </si>
+  <si>
+    <t>TIANHUI 6B</t>
+  </si>
+  <si>
+    <t>55839U</t>
+  </si>
+  <si>
+    <t>GEESAT 2-09</t>
+  </si>
+  <si>
+    <t>58913U</t>
+  </si>
+  <si>
+    <t>63345U</t>
+  </si>
+  <si>
+    <t>YUNYAQ-1 44</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,8 +229,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -246,6 +262,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -259,11 +281,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -917,11 +943,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2806803F-56BF-4E65-BE1E-5B4E77DD970E}">
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
@@ -961,191 +987,221 @@
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="1">
-        <v>2.79</v>
+        <v>2.94</v>
       </c>
       <c r="D3" s="1">
-        <v>3.93</v>
+        <v>3.71</v>
       </c>
       <c r="E3" s="1">
         <f>SUM(C3,D3)</f>
-        <v>6.7200000000000006</v>
+        <v>6.65</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="B4" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="C4">
-        <v>12.17</v>
+        <v>8.64</v>
       </c>
       <c r="D4">
-        <v>4.9000000000000004</v>
+        <v>4.84</v>
       </c>
       <c r="E4">
-        <f t="shared" ref="E4:E22" si="0">SUM(C4,D4)</f>
-        <v>17.07</v>
+        <f t="shared" ref="E4:E11" si="0">SUM(C4,D4)</f>
+        <v>13.48</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
       </c>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="C5" s="1">
-        <v>19.28</v>
+        <v>21</v>
       </c>
       <c r="D5" s="1">
-        <v>4.01</v>
+        <v>3.45</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>23.29</v>
+        <v>24.45</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G5" s="6"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="B6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C6">
-        <v>25.35</v>
+        <v>26.98</v>
       </c>
       <c r="D6">
-        <v>3.96</v>
+        <v>4.37</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>29.310000000000002</v>
+        <v>31.35</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
       </c>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="1">
-        <v>32.81</v>
-      </c>
-      <c r="D7" s="1">
-        <v>4.46</v>
+        <v>46</v>
+      </c>
+      <c r="C7" s="4">
+        <v>33.36</v>
+      </c>
+      <c r="D7" s="4">
+        <v>4.59</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>37.270000000000003</v>
+        <v>37.950000000000003</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G7" s="6"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C8">
-        <v>39.31</v>
+        <v>41.01</v>
       </c>
       <c r="D8">
-        <v>5.32</v>
+        <v>5.33</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>44.63</v>
+        <v>46.339999999999996</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
       </c>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>50</v>
       </c>
       <c r="C9" s="1">
-        <v>47.51</v>
+        <v>55.05</v>
       </c>
       <c r="D9" s="1">
-        <v>6.07</v>
+        <v>7.79</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="0"/>
-        <v>53.58</v>
+        <v>62.839999999999996</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G9" s="6"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C10">
-        <v>57.14</v>
+        <v>64.069999999999993</v>
       </c>
       <c r="D10">
-        <v>6.98</v>
+        <v>5.92</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>64.12</v>
+        <v>69.989999999999995</v>
       </c>
       <c r="F10" t="s">
         <v>10</v>
       </c>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C11" s="1">
-        <v>69.22</v>
+        <v>81.3</v>
       </c>
       <c r="D11" s="1">
-        <v>5.22</v>
+        <v>6.67</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="0"/>
-        <v>74.44</v>
+        <v>87.97</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>9</v>
+      </c>
+      <c r="G11" s="6"/>
+    </row>
+    <row r="12" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C12" s="7">
+        <v>99.26</v>
+      </c>
+      <c r="D12" s="7">
+        <v>5.21</v>
+      </c>
+      <c r="E12" s="7">
+        <f>SUM(C12,D12)</f>
+        <v>104.47</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/messplan.xlsx
+++ b/messplan.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Desktop\Studium\Laufend\Mechatronik und Leistungselektronik Projekt VU\project_code\orbitalPropagatorComparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF350AAF-77BC-468D-9C65-13B2665327A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDB6DBA-C083-4AAF-9DCB-A88C5237BAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Monday_19JAN2026UTC15_55" sheetId="1" r:id="rId1"/>
     <sheet name="Tuesday_20_JAN2026UTC16_00" sheetId="2" r:id="rId2"/>
-    <sheet name="Wednesday_17FEB2026UTC04_00" sheetId="3" r:id="rId3"/>
+    <sheet name="Friday_13MAR2026UTC16_45" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
   <si>
     <t>Satellite</t>
   </si>
@@ -157,64 +157,88 @@
     <t>Blinderfleck dabei, aber sonst gut</t>
   </si>
   <si>
-    <t>OBJECT B</t>
-  </si>
-  <si>
-    <t>49316U</t>
-  </si>
-  <si>
-    <t>CSG-1</t>
-  </si>
-  <si>
-    <t>44873U</t>
-  </si>
-  <si>
-    <t>COSMO SKYMED FM3</t>
-  </si>
-  <si>
-    <t>67304U</t>
-  </si>
-  <si>
-    <t>SAOCOM 1-A</t>
-  </si>
-  <si>
-    <t>43641U</t>
-  </si>
-  <si>
-    <t>SARAL</t>
-  </si>
-  <si>
-    <t>39086U</t>
-  </si>
-  <si>
-    <t>COSMOS 2355</t>
-  </si>
-  <si>
-    <t>25366U</t>
-  </si>
-  <si>
-    <t>YUNHAI 3-02</t>
-  </si>
-  <si>
-    <t>59343U</t>
-  </si>
-  <si>
-    <t>TIANHUI 6B</t>
-  </si>
-  <si>
-    <t>55839U</t>
-  </si>
-  <si>
-    <t>GEESAT 2-09</t>
-  </si>
-  <si>
-    <t>58913U</t>
-  </si>
-  <si>
-    <t>63345U</t>
-  </si>
-  <si>
-    <t>YUNYAQ-1 44</t>
+    <t>Friday 13.03.2026, 16:45 UTC</t>
+  </si>
+  <si>
+    <t>OBJECT A</t>
+  </si>
+  <si>
+    <t>61238U</t>
+  </si>
+  <si>
+    <t>CZ-6A DEB</t>
+  </si>
+  <si>
+    <t>54586U</t>
+  </si>
+  <si>
+    <t>SJ-12</t>
+  </si>
+  <si>
+    <t>36596U</t>
+  </si>
+  <si>
+    <t>07594U</t>
+  </si>
+  <si>
+    <t>COSMOS 1375 DEB</t>
+  </si>
+  <si>
+    <t>16210U</t>
+  </si>
+  <si>
+    <t>SL-14 R/B</t>
+  </si>
+  <si>
+    <t>16792U</t>
+  </si>
+  <si>
+    <t>GEESAT 6-05</t>
+  </si>
+  <si>
+    <t>65717U</t>
+  </si>
+  <si>
+    <t>KINEIS-1C</t>
+  </si>
+  <si>
+    <t>60081U</t>
+  </si>
+  <si>
+    <t>NOAA 9</t>
+  </si>
+  <si>
+    <t>15427U</t>
+  </si>
+  <si>
+    <t>COSMOS 1992</t>
+  </si>
+  <si>
+    <t>19769U</t>
+  </si>
+  <si>
+    <t>DIWATA 2B</t>
+  </si>
+  <si>
+    <t>43678U</t>
+  </si>
+  <si>
+    <t>COSMOS 2506</t>
+  </si>
+  <si>
+    <t>40699U</t>
+  </si>
+  <si>
+    <t>YUNHAI 2-1D</t>
+  </si>
+  <si>
+    <t>43912U</t>
+  </si>
+  <si>
+    <t>NOVA 1</t>
+  </si>
+  <si>
+    <t>12458U</t>
   </si>
 </sst>
 </file>
@@ -281,14 +305,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -943,7 +966,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2806803F-56BF-4E65-BE1E-5B4E77DD970E}">
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H16"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26.88671875" bestFit="1" customWidth="1"/>
@@ -952,11 +975,12 @@
     <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -987,42 +1011,42 @@
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1">
-        <v>2.94</v>
+        <v>0.79</v>
       </c>
       <c r="D3" s="1">
-        <v>3.71</v>
+        <v>3.44</v>
       </c>
       <c r="E3" s="1">
         <f>SUM(C3,D3)</f>
-        <v>6.65</v>
+        <v>4.2300000000000004</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="6"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C4">
-        <v>8.64</v>
+        <v>5.59</v>
       </c>
       <c r="D4">
-        <v>4.84</v>
+        <v>6.44</v>
       </c>
       <c r="E4">
         <f t="shared" ref="E4:E11" si="0">SUM(C4,D4)</f>
-        <v>13.48</v>
+        <v>12.030000000000001</v>
       </c>
       <c r="F4" t="s">
         <v>10</v>
@@ -1031,42 +1055,42 @@
     </row>
     <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C5" s="1">
-        <v>21</v>
+        <v>13.82</v>
       </c>
       <c r="D5" s="1">
-        <v>3.45</v>
+        <v>3.9</v>
       </c>
       <c r="E5" s="1">
         <f t="shared" si="0"/>
-        <v>24.45</v>
+        <v>17.72</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="6"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C6">
-        <v>26.98</v>
+        <v>18.72</v>
       </c>
       <c r="D6">
-        <v>4.37</v>
+        <v>6.9</v>
       </c>
       <c r="E6">
         <f t="shared" si="0"/>
-        <v>31.35</v>
+        <v>25.619999999999997</v>
       </c>
       <c r="F6" t="s">
         <v>10</v>
@@ -1075,42 +1099,42 @@
     </row>
     <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C7" s="4">
-        <v>33.36</v>
+        <v>26.7</v>
       </c>
       <c r="D7" s="4">
-        <v>4.59</v>
+        <v>5.47</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="0"/>
-        <v>37.950000000000003</v>
+        <v>32.17</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="6"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C8">
-        <v>41.01</v>
+        <v>33.840000000000003</v>
       </c>
       <c r="D8">
-        <v>5.33</v>
+        <v>4.87</v>
       </c>
       <c r="E8">
         <f t="shared" si="0"/>
-        <v>46.339999999999996</v>
+        <v>38.71</v>
       </c>
       <c r="F8" t="s">
         <v>10</v>
@@ -1119,42 +1143,42 @@
     </row>
     <row r="9" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1">
-        <v>55.05</v>
+        <v>40.47</v>
       </c>
       <c r="D9" s="1">
-        <v>7.79</v>
+        <v>4.99</v>
       </c>
       <c r="E9" s="1">
         <f t="shared" si="0"/>
-        <v>62.839999999999996</v>
+        <v>45.46</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="6"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C10">
-        <v>64.069999999999993</v>
+        <v>48.91</v>
       </c>
       <c r="D10">
-        <v>5.92</v>
+        <v>4.75</v>
       </c>
       <c r="E10">
         <f t="shared" si="0"/>
-        <v>69.989999999999995</v>
+        <v>53.66</v>
       </c>
       <c r="F10" t="s">
         <v>10</v>
@@ -1163,44 +1187,129 @@
     </row>
     <row r="11" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C11" s="1">
-        <v>81.3</v>
+        <v>55.57</v>
       </c>
       <c r="D11" s="1">
-        <v>6.67</v>
+        <v>5.98</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="0"/>
-        <v>87.97</v>
+        <v>61.55</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G11" s="6"/>
-    </row>
-    <row r="12" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C12" s="7">
-        <v>99.26</v>
-      </c>
-      <c r="D12" s="7">
-        <v>5.21</v>
-      </c>
-      <c r="E12" s="7">
+      <c r="G11" s="5"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C12">
+        <v>63.14</v>
+      </c>
+      <c r="D12">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="E12">
         <f>SUM(C12,D12)</f>
-        <v>104.47</v>
-      </c>
-      <c r="F12" s="7" t="s">
+        <v>67.540000000000006</v>
+      </c>
+      <c r="F12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G12" s="6"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="1">
+        <v>71.290000000000006</v>
+      </c>
+      <c r="D13" s="1">
+        <v>4.25</v>
+      </c>
+      <c r="E13" s="1">
+        <f>SUM(C13,D13)</f>
+        <v>75.540000000000006</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>61</v>
+      </c>
+      <c r="B14" t="s">
+        <v>62</v>
+      </c>
+      <c r="C14">
+        <v>80.34</v>
+      </c>
+      <c r="D14">
+        <v>4.6100000000000003</v>
+      </c>
+      <c r="E14">
+        <f>SUM(C14,D14)</f>
+        <v>84.95</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C15" s="1">
+        <v>88.56</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5.83</v>
+      </c>
+      <c r="E15" s="1">
+        <f>SUM(C15,D15)</f>
+        <v>94.39</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>65</v>
+      </c>
+      <c r="B16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16">
+        <v>96.93</v>
+      </c>
+      <c r="D16">
+        <v>7.05</v>
+      </c>
+      <c r="E16">
+        <f>SUM(C16,D16)</f>
+        <v>103.98</v>
+      </c>
+      <c r="F16" t="s">
         <v>10</v>
       </c>
     </row>

--- a/messplan.xlsx
+++ b/messplan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alexa\Desktop\Studium\Laufend\Mechatronik und Leistungselektronik Projekt VU\project_code\orbitalPropagatorComparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCDB6DBA-C083-4AAF-9DCB-A88C5237BAE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CF23D6B-A2F3-4C4F-B480-34A0D1F309BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
   <si>
     <t>Satellite</t>
   </si>
@@ -239,6 +239,21 @@
   </si>
   <si>
     <t>12458U</t>
+  </si>
+  <si>
+    <t>probleme mit der belichtungszeit</t>
+  </si>
+  <si>
+    <t>still some troubles, but needs checking, debris might be too dark simply</t>
+  </si>
+  <si>
+    <t>nice track</t>
+  </si>
+  <si>
+    <t>satellite only at beginning, moves out of field</t>
+  </si>
+  <si>
+    <t>satellite moves out of frame</t>
   </si>
 </sst>
 </file>
@@ -261,7 +276,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,6 +307,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -305,14 +344,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -975,7 +1019,7 @@
     <col min="5" max="5" width="17.109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="59.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
@@ -1029,7 +1073,10 @@
       <c r="F3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="5"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1051,7 +1098,10 @@
       <c r="F4" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="5"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="8" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="5" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -1073,7 +1123,10 @@
       <c r="F5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G5" s="5"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1095,7 +1148,10 @@
       <c r="F6" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="5"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="8" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="7" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -1117,7 +1173,10 @@
       <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G7" s="5"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="1" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1139,7 +1198,10 @@
       <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G8" s="5"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="8" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="9" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -1161,7 +1223,10 @@
       <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G9" s="5"/>
+      <c r="G9" s="10"/>
+      <c r="H9" s="1" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1183,7 +1248,10 @@
       <c r="F10" t="s">
         <v>10</v>
       </c>
-      <c r="G10" s="5"/>
+      <c r="G10" s="10"/>
+      <c r="H10" s="8" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="11" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
@@ -1227,9 +1295,8 @@
       <c r="F12" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="6"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>59</v>
       </c>
@@ -1270,8 +1337,9 @@
       <c r="F14" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>63</v>
       </c>
@@ -1291,6 +1359,7 @@
       <c r="F15" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
